--- a/plate3d/PLATE3D_INCHEON.xlsx
+++ b/plate3d/PLATE3D_INCHEON.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3483" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3587" uniqueCount="111">
   <si>
     <t>INCHEON BRIDGE  ·  800 m main span, 230.5 m pylons, 208 stays  ·  mm, Z up</t>
   </si>
@@ -16282,13 +16282,13 @@
         <v>3</v>
       </c>
       <c r="F364">
-        <v>-401300</v>
+        <v>-396360</v>
       </c>
       <c r="G364">
         <v>-700</v>
       </c>
       <c r="H364">
-        <v>230600</v>
+        <v>189800</v>
       </c>
       <c r="I364">
         <v>-377500</v>
@@ -16299,8 +16299,8 @@
       <c r="K364">
         <v>76954</v>
       </c>
-      <c r="L364">
-        <v>34659.3</v>
+      <c r="L364" t="s">
+        <v>3</v>
       </c>
       <c r="M364">
         <v>400</v>
@@ -16326,13 +16326,13 @@
         <v>3</v>
       </c>
       <c r="F365">
-        <v>-401300</v>
+        <v>-396360</v>
       </c>
       <c r="G365">
         <v>700</v>
       </c>
       <c r="H365">
-        <v>230600</v>
+        <v>189800</v>
       </c>
       <c r="I365">
         <v>-377500</v>
@@ -16343,8 +16343,8 @@
       <c r="K365">
         <v>76954</v>
       </c>
-      <c r="L365">
-        <v>34659.3</v>
+      <c r="L365" t="s">
+        <v>3</v>
       </c>
       <c r="M365">
         <v>400</v>
@@ -16370,13 +16370,13 @@
         <v>3</v>
       </c>
       <c r="F366">
-        <v>-400000</v>
+        <v>-396360</v>
       </c>
       <c r="G366">
         <v>-700</v>
       </c>
       <c r="H366">
-        <v>228968</v>
+        <v>191432</v>
       </c>
       <c r="I366">
         <v>-366250</v>
@@ -16387,8 +16387,8 @@
       <c r="K366">
         <v>76954</v>
       </c>
-      <c r="L366">
-        <v>18451.3</v>
+      <c r="L366" t="s">
+        <v>3</v>
       </c>
       <c r="M366">
         <v>400</v>
@@ -16414,13 +16414,13 @@
         <v>3</v>
       </c>
       <c r="F367">
-        <v>-400000</v>
+        <v>-396360</v>
       </c>
       <c r="G367">
         <v>700</v>
       </c>
       <c r="H367">
-        <v>228968</v>
+        <v>191432</v>
       </c>
       <c r="I367">
         <v>-366250</v>
@@ -16431,8 +16431,8 @@
       <c r="K367">
         <v>76954</v>
       </c>
-      <c r="L367">
-        <v>18451.3</v>
+      <c r="L367" t="s">
+        <v>3</v>
       </c>
       <c r="M367">
         <v>400</v>
@@ -16458,13 +16458,13 @@
         <v>3</v>
       </c>
       <c r="F368">
-        <v>-398700</v>
+        <v>-396360</v>
       </c>
       <c r="G368">
         <v>-700</v>
       </c>
       <c r="H368">
-        <v>227336</v>
+        <v>193064</v>
       </c>
       <c r="I368">
         <v>-355000</v>
@@ -16475,8 +16475,8 @@
       <c r="K368">
         <v>76954</v>
       </c>
-      <c r="L368">
-        <v>9649.7</v>
+      <c r="L368" t="s">
+        <v>3</v>
       </c>
       <c r="M368">
         <v>400</v>
@@ -16502,13 +16502,13 @@
         <v>3</v>
       </c>
       <c r="F369">
-        <v>-398700</v>
+        <v>-396360</v>
       </c>
       <c r="G369">
         <v>700</v>
       </c>
       <c r="H369">
-        <v>227336</v>
+        <v>193064</v>
       </c>
       <c r="I369">
         <v>-355000</v>
@@ -16519,8 +16519,8 @@
       <c r="K369">
         <v>76954</v>
       </c>
-      <c r="L369">
-        <v>9649.7</v>
+      <c r="L369" t="s">
+        <v>3</v>
       </c>
       <c r="M369">
         <v>400</v>
@@ -16546,13 +16546,13 @@
         <v>3</v>
       </c>
       <c r="F370">
-        <v>-401300</v>
+        <v>-396360</v>
       </c>
       <c r="G370">
         <v>-700</v>
       </c>
       <c r="H370">
-        <v>225704</v>
+        <v>194696</v>
       </c>
       <c r="I370">
         <v>-340000</v>
@@ -16563,8 +16563,8 @@
       <c r="K370">
         <v>76954</v>
       </c>
-      <c r="L370">
-        <v>13920.2</v>
+      <c r="L370" t="s">
+        <v>3</v>
       </c>
       <c r="M370">
         <v>400</v>
@@ -16590,13 +16590,13 @@
         <v>3</v>
       </c>
       <c r="F371">
-        <v>-401300</v>
+        <v>-396360</v>
       </c>
       <c r="G371">
         <v>700</v>
       </c>
       <c r="H371">
-        <v>225704</v>
+        <v>194696</v>
       </c>
       <c r="I371">
         <v>-340000</v>
@@ -16607,8 +16607,8 @@
       <c r="K371">
         <v>76954</v>
       </c>
-      <c r="L371">
-        <v>13920.2</v>
+      <c r="L371" t="s">
+        <v>3</v>
       </c>
       <c r="M371">
         <v>400</v>
@@ -16634,13 +16634,13 @@
         <v>3</v>
       </c>
       <c r="F372">
-        <v>-400000</v>
+        <v>-396360</v>
       </c>
       <c r="G372">
         <v>-700</v>
       </c>
       <c r="H372">
-        <v>224072</v>
+        <v>196328</v>
       </c>
       <c r="I372">
         <v>-325000</v>
@@ -16651,8 +16651,8 @@
       <c r="K372">
         <v>76954</v>
       </c>
-      <c r="L372">
-        <v>8800.6</v>
+      <c r="L372" t="s">
+        <v>3</v>
       </c>
       <c r="M372">
         <v>400</v>
@@ -16678,13 +16678,13 @@
         <v>3</v>
       </c>
       <c r="F373">
-        <v>-400000</v>
+        <v>-396360</v>
       </c>
       <c r="G373">
         <v>700</v>
       </c>
       <c r="H373">
-        <v>224072</v>
+        <v>196328</v>
       </c>
       <c r="I373">
         <v>-325000</v>
@@ -16695,8 +16695,8 @@
       <c r="K373">
         <v>76954</v>
       </c>
-      <c r="L373">
-        <v>8800.6</v>
+      <c r="L373" t="s">
+        <v>3</v>
       </c>
       <c r="M373">
         <v>400</v>
@@ -16722,13 +16722,13 @@
         <v>3</v>
       </c>
       <c r="F374">
-        <v>-398700</v>
+        <v>-396360</v>
       </c>
       <c r="G374">
         <v>-700</v>
       </c>
       <c r="H374">
-        <v>222440</v>
+        <v>197960</v>
       </c>
       <c r="I374">
         <v>-310000</v>
@@ -16739,8 +16739,8 @@
       <c r="K374">
         <v>76954</v>
       </c>
-      <c r="L374">
-        <v>5169</v>
+      <c r="L374" t="s">
+        <v>3</v>
       </c>
       <c r="M374">
         <v>400</v>
@@ -16766,13 +16766,13 @@
         <v>3</v>
       </c>
       <c r="F375">
-        <v>-398700</v>
+        <v>-396360</v>
       </c>
       <c r="G375">
         <v>700</v>
       </c>
       <c r="H375">
-        <v>222440</v>
+        <v>197960</v>
       </c>
       <c r="I375">
         <v>-310000</v>
@@ -16783,8 +16783,8 @@
       <c r="K375">
         <v>76954</v>
       </c>
-      <c r="L375">
-        <v>5169</v>
+      <c r="L375" t="s">
+        <v>3</v>
       </c>
       <c r="M375">
         <v>400</v>
@@ -16810,13 +16810,13 @@
         <v>3</v>
       </c>
       <c r="F376">
-        <v>-401300</v>
+        <v>-396360</v>
       </c>
       <c r="G376">
         <v>-700</v>
       </c>
       <c r="H376">
-        <v>220808</v>
+        <v>199592</v>
       </c>
       <c r="I376">
         <v>-295000</v>
@@ -16827,8 +16827,8 @@
       <c r="K376">
         <v>76954</v>
       </c>
-      <c r="L376">
-        <v>8916.9</v>
+      <c r="L376" t="s">
+        <v>3</v>
       </c>
       <c r="M376">
         <v>400</v>
@@ -16854,13 +16854,13 @@
         <v>3</v>
       </c>
       <c r="F377">
-        <v>-401300</v>
+        <v>-396360</v>
       </c>
       <c r="G377">
         <v>700</v>
       </c>
       <c r="H377">
-        <v>220808</v>
+        <v>199592</v>
       </c>
       <c r="I377">
         <v>-295000</v>
@@ -16871,8 +16871,8 @@
       <c r="K377">
         <v>76954</v>
       </c>
-      <c r="L377">
-        <v>8916.9</v>
+      <c r="L377" t="s">
+        <v>3</v>
       </c>
       <c r="M377">
         <v>400</v>
@@ -16898,13 +16898,13 @@
         <v>3</v>
       </c>
       <c r="F378">
-        <v>-400000</v>
+        <v>-396360</v>
       </c>
       <c r="G378">
         <v>-700</v>
       </c>
       <c r="H378">
-        <v>219176</v>
+        <v>201224</v>
       </c>
       <c r="I378">
         <v>-280000</v>
@@ -16915,8 +16915,8 @@
       <c r="K378">
         <v>76954</v>
       </c>
-      <c r="L378">
-        <v>6192.6</v>
+      <c r="L378" t="s">
+        <v>3</v>
       </c>
       <c r="M378">
         <v>400</v>
@@ -16942,13 +16942,13 @@
         <v>3</v>
       </c>
       <c r="F379">
-        <v>-400000</v>
+        <v>-396360</v>
       </c>
       <c r="G379">
         <v>700</v>
       </c>
       <c r="H379">
-        <v>219176</v>
+        <v>201224</v>
       </c>
       <c r="I379">
         <v>-280000</v>
@@ -16959,8 +16959,8 @@
       <c r="K379">
         <v>76954</v>
       </c>
-      <c r="L379">
-        <v>6192.6</v>
+      <c r="L379" t="s">
+        <v>3</v>
       </c>
       <c r="M379">
         <v>400</v>
@@ -16986,13 +16986,13 @@
         <v>3</v>
       </c>
       <c r="F380">
-        <v>-398700</v>
+        <v>-396360</v>
       </c>
       <c r="G380">
         <v>-700</v>
       </c>
       <c r="H380">
-        <v>217544</v>
+        <v>202856</v>
       </c>
       <c r="I380">
         <v>-265000</v>
@@ -17003,8 +17003,8 @@
       <c r="K380">
         <v>76954</v>
       </c>
-      <c r="L380">
-        <v>3901.1</v>
+      <c r="L380" t="s">
+        <v>3</v>
       </c>
       <c r="M380">
         <v>400</v>
@@ -17030,13 +17030,13 @@
         <v>3</v>
       </c>
       <c r="F381">
-        <v>-398700</v>
+        <v>-396360</v>
       </c>
       <c r="G381">
         <v>700</v>
       </c>
       <c r="H381">
-        <v>217544</v>
+        <v>202856</v>
       </c>
       <c r="I381">
         <v>-265000</v>
@@ -17047,8 +17047,8 @@
       <c r="K381">
         <v>76954</v>
       </c>
-      <c r="L381">
-        <v>3901.1</v>
+      <c r="L381" t="s">
+        <v>3</v>
       </c>
       <c r="M381">
         <v>400</v>
@@ -17074,13 +17074,13 @@
         <v>3</v>
       </c>
       <c r="F382">
-        <v>-401300</v>
+        <v>-396360</v>
       </c>
       <c r="G382">
         <v>-700</v>
       </c>
       <c r="H382">
-        <v>215912</v>
+        <v>204488</v>
       </c>
       <c r="I382">
         <v>-250000</v>
@@ -17091,8 +17091,8 @@
       <c r="K382">
         <v>76954</v>
       </c>
-      <c r="L382">
-        <v>7188.8</v>
+      <c r="L382" t="s">
+        <v>3</v>
       </c>
       <c r="M382">
         <v>400</v>
@@ -17118,13 +17118,13 @@
         <v>3</v>
       </c>
       <c r="F383">
-        <v>-401300</v>
+        <v>-396360</v>
       </c>
       <c r="G383">
         <v>700</v>
       </c>
       <c r="H383">
-        <v>215912</v>
+        <v>204488</v>
       </c>
       <c r="I383">
         <v>-250000</v>
@@ -17135,8 +17135,8 @@
       <c r="K383">
         <v>76954</v>
       </c>
-      <c r="L383">
-        <v>7188.8</v>
+      <c r="L383" t="s">
+        <v>3</v>
       </c>
       <c r="M383">
         <v>400</v>
@@ -17162,13 +17162,13 @@
         <v>3</v>
       </c>
       <c r="F384">
-        <v>-400000</v>
+        <v>-396360</v>
       </c>
       <c r="G384">
         <v>-700</v>
       </c>
       <c r="H384">
-        <v>214280</v>
+        <v>206120</v>
       </c>
       <c r="I384">
         <v>-235000</v>
@@ -17179,8 +17179,8 @@
       <c r="K384">
         <v>76954</v>
       </c>
-      <c r="L384">
-        <v>5191.2</v>
+      <c r="L384" t="s">
+        <v>3</v>
       </c>
       <c r="M384">
         <v>400</v>
@@ -17206,13 +17206,13 @@
         <v>3</v>
       </c>
       <c r="F385">
-        <v>-400000</v>
+        <v>-396360</v>
       </c>
       <c r="G385">
         <v>700</v>
       </c>
       <c r="H385">
-        <v>214280</v>
+        <v>206120</v>
       </c>
       <c r="I385">
         <v>-235000</v>
@@ -17223,8 +17223,8 @@
       <c r="K385">
         <v>76954</v>
       </c>
-      <c r="L385">
-        <v>5191.2</v>
+      <c r="L385" t="s">
+        <v>3</v>
       </c>
       <c r="M385">
         <v>400</v>
@@ -17250,13 +17250,13 @@
         <v>3</v>
       </c>
       <c r="F386">
-        <v>-398700</v>
+        <v>-396360</v>
       </c>
       <c r="G386">
         <v>-700</v>
       </c>
       <c r="H386">
-        <v>212648</v>
+        <v>207752</v>
       </c>
       <c r="I386">
         <v>-220000</v>
@@ -17267,8 +17267,8 @@
       <c r="K386">
         <v>76954</v>
       </c>
-      <c r="L386">
-        <v>3372.9</v>
+      <c r="L386" t="s">
+        <v>3</v>
       </c>
       <c r="M386">
         <v>400</v>
@@ -17294,13 +17294,13 @@
         <v>3</v>
       </c>
       <c r="F387">
-        <v>-398700</v>
+        <v>-396360</v>
       </c>
       <c r="G387">
         <v>700</v>
       </c>
       <c r="H387">
-        <v>212648</v>
+        <v>207752</v>
       </c>
       <c r="I387">
         <v>-220000</v>
@@ -17311,8 +17311,8 @@
       <c r="K387">
         <v>76954</v>
       </c>
-      <c r="L387">
-        <v>3372.9</v>
+      <c r="L387" t="s">
+        <v>3</v>
       </c>
       <c r="M387">
         <v>400</v>
@@ -17338,13 +17338,13 @@
         <v>3</v>
       </c>
       <c r="F388">
-        <v>-401300</v>
+        <v>-396360</v>
       </c>
       <c r="G388">
         <v>-700</v>
       </c>
       <c r="H388">
-        <v>211016</v>
+        <v>209384</v>
       </c>
       <c r="I388">
         <v>-205000</v>
@@ -17355,8 +17355,8 @@
       <c r="K388">
         <v>76954</v>
       </c>
-      <c r="L388">
-        <v>6407.1</v>
+      <c r="L388" t="s">
+        <v>3</v>
       </c>
       <c r="M388">
         <v>400</v>
@@ -17382,13 +17382,13 @@
         <v>3</v>
       </c>
       <c r="F389">
-        <v>-401300</v>
+        <v>-396360</v>
       </c>
       <c r="G389">
         <v>700</v>
       </c>
       <c r="H389">
-        <v>211016</v>
+        <v>209384</v>
       </c>
       <c r="I389">
         <v>-205000</v>
@@ -17399,8 +17399,8 @@
       <c r="K389">
         <v>76954</v>
       </c>
-      <c r="L389">
-        <v>6407.1</v>
+      <c r="L389" t="s">
+        <v>3</v>
       </c>
       <c r="M389">
         <v>400</v>
@@ -17426,13 +17426,13 @@
         <v>3</v>
       </c>
       <c r="F390">
-        <v>-400000</v>
+        <v>-396340</v>
       </c>
       <c r="G390">
         <v>-700</v>
       </c>
       <c r="H390">
-        <v>209384</v>
+        <v>211016</v>
       </c>
       <c r="I390">
         <v>-190000</v>
@@ -17443,8 +17443,8 @@
       <c r="K390">
         <v>76954</v>
       </c>
-      <c r="L390">
-        <v>4737.9</v>
+      <c r="L390" t="s">
+        <v>3</v>
       </c>
       <c r="M390">
         <v>400</v>
@@ -17470,13 +17470,13 @@
         <v>3</v>
       </c>
       <c r="F391">
-        <v>-400000</v>
+        <v>-396340</v>
       </c>
       <c r="G391">
         <v>700</v>
       </c>
       <c r="H391">
-        <v>209384</v>
+        <v>211016</v>
       </c>
       <c r="I391">
         <v>-190000</v>
@@ -17487,8 +17487,8 @@
       <c r="K391">
         <v>76954</v>
       </c>
-      <c r="L391">
-        <v>4737.9</v>
+      <c r="L391" t="s">
+        <v>3</v>
       </c>
       <c r="M391">
         <v>400</v>
@@ -17514,13 +17514,13 @@
         <v>3</v>
       </c>
       <c r="F392">
-        <v>-398700</v>
+        <v>-396340</v>
       </c>
       <c r="G392">
         <v>-700</v>
       </c>
       <c r="H392">
-        <v>207752</v>
+        <v>212648</v>
       </c>
       <c r="I392">
         <v>-175000</v>
@@ -17531,8 +17531,8 @@
       <c r="K392">
         <v>76954</v>
       </c>
-      <c r="L392">
-        <v>3133.1</v>
+      <c r="L392" t="s">
+        <v>3</v>
       </c>
       <c r="M392">
         <v>400</v>
@@ -17558,13 +17558,13 @@
         <v>3</v>
       </c>
       <c r="F393">
-        <v>-398700</v>
+        <v>-396340</v>
       </c>
       <c r="G393">
         <v>700</v>
       </c>
       <c r="H393">
-        <v>207752</v>
+        <v>212648</v>
       </c>
       <c r="I393">
         <v>-175000</v>
@@ -17575,8 +17575,8 @@
       <c r="K393">
         <v>76954</v>
       </c>
-      <c r="L393">
-        <v>3133.1</v>
+      <c r="L393" t="s">
+        <v>3</v>
       </c>
       <c r="M393">
         <v>400</v>
@@ -17602,13 +17602,13 @@
         <v>3</v>
       </c>
       <c r="F394">
-        <v>-401300</v>
+        <v>-396340</v>
       </c>
       <c r="G394">
         <v>-700</v>
       </c>
       <c r="H394">
-        <v>206120</v>
+        <v>214280</v>
       </c>
       <c r="I394">
         <v>-160000</v>
@@ -17619,8 +17619,8 @@
       <c r="K394">
         <v>76954</v>
       </c>
-      <c r="L394">
-        <v>6020.9</v>
+      <c r="L394" t="s">
+        <v>3</v>
       </c>
       <c r="M394">
         <v>400</v>
@@ -17646,13 +17646,13 @@
         <v>3</v>
       </c>
       <c r="F395">
-        <v>-401300</v>
+        <v>-396340</v>
       </c>
       <c r="G395">
         <v>700</v>
       </c>
       <c r="H395">
-        <v>206120</v>
+        <v>214280</v>
       </c>
       <c r="I395">
         <v>-160000</v>
@@ -17663,8 +17663,8 @@
       <c r="K395">
         <v>76954</v>
       </c>
-      <c r="L395">
-        <v>6020.9</v>
+      <c r="L395" t="s">
+        <v>3</v>
       </c>
       <c r="M395">
         <v>400</v>
@@ -17690,13 +17690,13 @@
         <v>3</v>
       </c>
       <c r="F396">
-        <v>-400000</v>
+        <v>-396340</v>
       </c>
       <c r="G396">
         <v>-700</v>
       </c>
       <c r="H396">
-        <v>204488</v>
+        <v>215912</v>
       </c>
       <c r="I396">
         <v>-145000</v>
@@ -17707,8 +17707,8 @@
       <c r="K396">
         <v>76954</v>
       </c>
-      <c r="L396">
-        <v>4478.8</v>
+      <c r="L396" t="s">
+        <v>3</v>
       </c>
       <c r="M396">
         <v>400</v>
@@ -17734,13 +17734,13 @@
         <v>3</v>
       </c>
       <c r="F397">
-        <v>-400000</v>
+        <v>-396340</v>
       </c>
       <c r="G397">
         <v>700</v>
       </c>
       <c r="H397">
-        <v>204488</v>
+        <v>215912</v>
       </c>
       <c r="I397">
         <v>-145000</v>
@@ -17751,8 +17751,8 @@
       <c r="K397">
         <v>76954</v>
       </c>
-      <c r="L397">
-        <v>4478.8</v>
+      <c r="L397" t="s">
+        <v>3</v>
       </c>
       <c r="M397">
         <v>400</v>
@@ -17778,13 +17778,13 @@
         <v>3</v>
       </c>
       <c r="F398">
-        <v>-398700</v>
+        <v>-396340</v>
       </c>
       <c r="G398">
         <v>-700</v>
       </c>
       <c r="H398">
-        <v>202856</v>
+        <v>217544</v>
       </c>
       <c r="I398">
         <v>-130000</v>
@@ -17795,8 +17795,8 @@
       <c r="K398">
         <v>76954</v>
       </c>
-      <c r="L398">
-        <v>2985.7</v>
+      <c r="L398" t="s">
+        <v>3</v>
       </c>
       <c r="M398">
         <v>400</v>
@@ -17822,13 +17822,13 @@
         <v>3</v>
       </c>
       <c r="F399">
-        <v>-398700</v>
+        <v>-396340</v>
       </c>
       <c r="G399">
         <v>700</v>
       </c>
       <c r="H399">
-        <v>202856</v>
+        <v>217544</v>
       </c>
       <c r="I399">
         <v>-130000</v>
@@ -17839,8 +17839,8 @@
       <c r="K399">
         <v>76954</v>
       </c>
-      <c r="L399">
-        <v>2985.7</v>
+      <c r="L399" t="s">
+        <v>3</v>
       </c>
       <c r="M399">
         <v>400</v>
@@ -17866,13 +17866,13 @@
         <v>3</v>
       </c>
       <c r="F400">
-        <v>-401300</v>
+        <v>-396340</v>
       </c>
       <c r="G400">
         <v>-700</v>
       </c>
       <c r="H400">
-        <v>201224</v>
+        <v>219176</v>
       </c>
       <c r="I400">
         <v>-115000</v>
@@ -17883,8 +17883,8 @@
       <c r="K400">
         <v>76954</v>
       </c>
-      <c r="L400">
-        <v>5784.7</v>
+      <c r="L400" t="s">
+        <v>3</v>
       </c>
       <c r="M400">
         <v>400</v>
@@ -17910,13 +17910,13 @@
         <v>3</v>
       </c>
       <c r="F401">
-        <v>-401300</v>
+        <v>-396340</v>
       </c>
       <c r="G401">
         <v>700</v>
       </c>
       <c r="H401">
-        <v>201224</v>
+        <v>219176</v>
       </c>
       <c r="I401">
         <v>-115000</v>
@@ -17927,8 +17927,8 @@
       <c r="K401">
         <v>76954</v>
       </c>
-      <c r="L401">
-        <v>5784.7</v>
+      <c r="L401" t="s">
+        <v>3</v>
       </c>
       <c r="M401">
         <v>400</v>
@@ -17954,13 +17954,13 @@
         <v>3</v>
       </c>
       <c r="F402">
-        <v>-400000</v>
+        <v>-396340</v>
       </c>
       <c r="G402">
         <v>-700</v>
       </c>
       <c r="H402">
-        <v>199592</v>
+        <v>220808</v>
       </c>
       <c r="I402">
         <v>-100000</v>
@@ -17971,8 +17971,8 @@
       <c r="K402">
         <v>76954</v>
       </c>
-      <c r="L402">
-        <v>4326.1</v>
+      <c r="L402" t="s">
+        <v>3</v>
       </c>
       <c r="M402">
         <v>400</v>
@@ -17998,13 +17998,13 @@
         <v>3</v>
       </c>
       <c r="F403">
-        <v>-400000</v>
+        <v>-396340</v>
       </c>
       <c r="G403">
         <v>700</v>
       </c>
       <c r="H403">
-        <v>199592</v>
+        <v>220808</v>
       </c>
       <c r="I403">
         <v>-100000</v>
@@ -18015,8 +18015,8 @@
       <c r="K403">
         <v>76954</v>
       </c>
-      <c r="L403">
-        <v>4326.1</v>
+      <c r="L403" t="s">
+        <v>3</v>
       </c>
       <c r="M403">
         <v>400</v>
@@ -18042,13 +18042,13 @@
         <v>3</v>
       </c>
       <c r="F404">
-        <v>-398700</v>
+        <v>-396340</v>
       </c>
       <c r="G404">
         <v>-700</v>
       </c>
       <c r="H404">
-        <v>197960</v>
+        <v>222440</v>
       </c>
       <c r="I404">
         <v>-85000</v>
@@ -18059,8 +18059,8 @@
       <c r="K404">
         <v>76954</v>
       </c>
-      <c r="L404">
-        <v>2896.9</v>
+      <c r="L404" t="s">
+        <v>3</v>
       </c>
       <c r="M404">
         <v>400</v>
@@ -18086,13 +18086,13 @@
         <v>3</v>
       </c>
       <c r="F405">
-        <v>-398700</v>
+        <v>-396340</v>
       </c>
       <c r="G405">
         <v>700</v>
       </c>
       <c r="H405">
-        <v>197960</v>
+        <v>222440</v>
       </c>
       <c r="I405">
         <v>-85000</v>
@@ -18103,8 +18103,8 @@
       <c r="K405">
         <v>76954</v>
       </c>
-      <c r="L405">
-        <v>2896.9</v>
+      <c r="L405" t="s">
+        <v>3</v>
       </c>
       <c r="M405">
         <v>400</v>
@@ -18130,13 +18130,13 @@
         <v>3</v>
       </c>
       <c r="F406">
-        <v>-401300</v>
+        <v>-396340</v>
       </c>
       <c r="G406">
         <v>-700</v>
       </c>
       <c r="H406">
-        <v>196328</v>
+        <v>224072</v>
       </c>
       <c r="I406">
         <v>-70000</v>
@@ -18147,8 +18147,8 @@
       <c r="K406">
         <v>76954</v>
       </c>
-      <c r="L406">
-        <v>5638.9</v>
+      <c r="L406" t="s">
+        <v>3</v>
       </c>
       <c r="M406">
         <v>400</v>
@@ -18174,13 +18174,13 @@
         <v>3</v>
       </c>
       <c r="F407">
-        <v>-401300</v>
+        <v>-396340</v>
       </c>
       <c r="G407">
         <v>700</v>
       </c>
       <c r="H407">
-        <v>196328</v>
+        <v>224072</v>
       </c>
       <c r="I407">
         <v>-70000</v>
@@ -18191,8 +18191,8 @@
       <c r="K407">
         <v>76954</v>
       </c>
-      <c r="L407">
-        <v>5638.9</v>
+      <c r="L407" t="s">
+        <v>3</v>
       </c>
       <c r="M407">
         <v>400</v>
@@ -18218,13 +18218,13 @@
         <v>3</v>
       </c>
       <c r="F408">
-        <v>-400000</v>
+        <v>-396340</v>
       </c>
       <c r="G408">
         <v>-700</v>
       </c>
       <c r="H408">
-        <v>194696</v>
+        <v>225704</v>
       </c>
       <c r="I408">
         <v>-55000</v>
@@ -18235,8 +18235,8 @@
       <c r="K408">
         <v>76954</v>
       </c>
-      <c r="L408">
-        <v>4230.3</v>
+      <c r="L408" t="s">
+        <v>3</v>
       </c>
       <c r="M408">
         <v>400</v>
@@ -18262,13 +18262,13 @@
         <v>3</v>
       </c>
       <c r="F409">
-        <v>-400000</v>
+        <v>-396340</v>
       </c>
       <c r="G409">
         <v>700</v>
       </c>
       <c r="H409">
-        <v>194696</v>
+        <v>225704</v>
       </c>
       <c r="I409">
         <v>-55000</v>
@@ -18279,8 +18279,8 @@
       <c r="K409">
         <v>76954</v>
       </c>
-      <c r="L409">
-        <v>4230.3</v>
+      <c r="L409" t="s">
+        <v>3</v>
       </c>
       <c r="M409">
         <v>400</v>
@@ -18306,13 +18306,13 @@
         <v>3</v>
       </c>
       <c r="F410">
-        <v>-398700</v>
+        <v>-396340</v>
       </c>
       <c r="G410">
         <v>-700</v>
       </c>
       <c r="H410">
-        <v>193064</v>
+        <v>227336</v>
       </c>
       <c r="I410">
         <v>-40000</v>
@@ -18323,8 +18323,8 @@
       <c r="K410">
         <v>76954</v>
       </c>
-      <c r="L410">
-        <v>2840.3</v>
+      <c r="L410" t="s">
+        <v>3</v>
       </c>
       <c r="M410">
         <v>400</v>
@@ -18350,13 +18350,13 @@
         <v>3</v>
       </c>
       <c r="F411">
-        <v>-398700</v>
+        <v>-396340</v>
       </c>
       <c r="G411">
         <v>700</v>
       </c>
       <c r="H411">
-        <v>193064</v>
+        <v>227336</v>
       </c>
       <c r="I411">
         <v>-40000</v>
@@ -18367,8 +18367,8 @@
       <c r="K411">
         <v>76954</v>
       </c>
-      <c r="L411">
-        <v>2840.3</v>
+      <c r="L411" t="s">
+        <v>3</v>
       </c>
       <c r="M411">
         <v>400</v>
@@ -18394,13 +18394,13 @@
         <v>3</v>
       </c>
       <c r="F412">
-        <v>-401300</v>
+        <v>-396340</v>
       </c>
       <c r="G412">
         <v>-700</v>
       </c>
       <c r="H412">
-        <v>191432</v>
+        <v>228968</v>
       </c>
       <c r="I412">
         <v>-25000</v>
@@ -18411,8 +18411,8 @@
       <c r="K412">
         <v>76954</v>
       </c>
-      <c r="L412">
-        <v>5544</v>
+      <c r="L412" t="s">
+        <v>3</v>
       </c>
       <c r="M412">
         <v>400</v>
@@ -18438,13 +18438,13 @@
         <v>3</v>
       </c>
       <c r="F413">
-        <v>-401300</v>
+        <v>-396340</v>
       </c>
       <c r="G413">
         <v>700</v>
       </c>
       <c r="H413">
-        <v>191432</v>
+        <v>228968</v>
       </c>
       <c r="I413">
         <v>-25000</v>
@@ -18455,8 +18455,8 @@
       <c r="K413">
         <v>76954</v>
       </c>
-      <c r="L413">
-        <v>5544</v>
+      <c r="L413" t="s">
+        <v>3</v>
       </c>
       <c r="M413">
         <v>400</v>
@@ -18482,13 +18482,13 @@
         <v>3</v>
       </c>
       <c r="F414">
-        <v>-400000</v>
+        <v>-396340</v>
       </c>
       <c r="G414">
         <v>-700</v>
       </c>
       <c r="H414">
-        <v>189800</v>
+        <v>230600</v>
       </c>
       <c r="I414">
         <v>-10000</v>
@@ -18499,8 +18499,8 @@
       <c r="K414">
         <v>76954</v>
       </c>
-      <c r="L414">
-        <v>4167</v>
+      <c r="L414" t="s">
+        <v>3</v>
       </c>
       <c r="M414">
         <v>400</v>
@@ -18526,13 +18526,13 @@
         <v>3</v>
       </c>
       <c r="F415">
-        <v>-400000</v>
+        <v>-396340</v>
       </c>
       <c r="G415">
         <v>700</v>
       </c>
       <c r="H415">
-        <v>189800</v>
+        <v>230600</v>
       </c>
       <c r="I415">
         <v>-10000</v>
@@ -18543,8 +18543,8 @@
       <c r="K415">
         <v>76954</v>
       </c>
-      <c r="L415">
-        <v>4167</v>
+      <c r="L415" t="s">
+        <v>3</v>
       </c>
       <c r="M415">
         <v>400</v>
@@ -18570,13 +18570,13 @@
         <v>3</v>
       </c>
       <c r="F416">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G416">
         <v>-700</v>
       </c>
       <c r="H416">
-        <v>230600</v>
+        <v>189800</v>
       </c>
       <c r="I416">
         <v>-422500</v>
@@ -18587,8 +18587,8 @@
       <c r="K416">
         <v>76954</v>
       </c>
-      <c r="L416">
-        <v>19849.4</v>
+      <c r="L416" t="s">
+        <v>3</v>
       </c>
       <c r="M416">
         <v>400</v>
@@ -18614,13 +18614,13 @@
         <v>3</v>
       </c>
       <c r="F417">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G417">
         <v>700</v>
       </c>
       <c r="H417">
-        <v>230600</v>
+        <v>189800</v>
       </c>
       <c r="I417">
         <v>-422500</v>
@@ -18631,8 +18631,8 @@
       <c r="K417">
         <v>76954</v>
       </c>
-      <c r="L417">
-        <v>19849.4</v>
+      <c r="L417" t="s">
+        <v>3</v>
       </c>
       <c r="M417">
         <v>400</v>
@@ -18658,13 +18658,13 @@
         <v>3</v>
       </c>
       <c r="F418">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G418">
         <v>-700</v>
       </c>
       <c r="H418">
-        <v>228968</v>
+        <v>191432</v>
       </c>
       <c r="I418">
         <v>-431480</v>
@@ -18675,8 +18675,8 @@
       <c r="K418">
         <v>76954</v>
       </c>
-      <c r="L418">
-        <v>19821</v>
+      <c r="L418" t="s">
+        <v>3</v>
       </c>
       <c r="M418">
         <v>400</v>
@@ -18702,13 +18702,13 @@
         <v>3</v>
       </c>
       <c r="F419">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G419">
         <v>700</v>
       </c>
       <c r="H419">
-        <v>228968</v>
+        <v>191432</v>
       </c>
       <c r="I419">
         <v>-431480</v>
@@ -18719,8 +18719,8 @@
       <c r="K419">
         <v>76954</v>
       </c>
-      <c r="L419">
-        <v>19821</v>
+      <c r="L419" t="s">
+        <v>3</v>
       </c>
       <c r="M419">
         <v>400</v>
@@ -18746,13 +18746,13 @@
         <v>3</v>
       </c>
       <c r="F420">
-        <v>-398700</v>
+        <v>-403660</v>
       </c>
       <c r="G420">
         <v>-700</v>
       </c>
       <c r="H420">
-        <v>227336</v>
+        <v>193064</v>
       </c>
       <c r="I420">
         <v>-440460</v>
@@ -18763,8 +18763,8 @@
       <c r="K420">
         <v>76954</v>
       </c>
-      <c r="L420">
-        <v>19903</v>
+      <c r="L420" t="s">
+        <v>3</v>
       </c>
       <c r="M420">
         <v>400</v>
@@ -18790,13 +18790,13 @@
         <v>3</v>
       </c>
       <c r="F421">
-        <v>-398700</v>
+        <v>-403660</v>
       </c>
       <c r="G421">
         <v>700</v>
       </c>
       <c r="H421">
-        <v>227336</v>
+        <v>193064</v>
       </c>
       <c r="I421">
         <v>-440460</v>
@@ -18807,8 +18807,8 @@
       <c r="K421">
         <v>76954</v>
       </c>
-      <c r="L421">
-        <v>19903</v>
+      <c r="L421" t="s">
+        <v>3</v>
       </c>
       <c r="M421">
         <v>400</v>
@@ -18834,13 +18834,13 @@
         <v>3</v>
       </c>
       <c r="F422">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G422">
         <v>-700</v>
       </c>
       <c r="H422">
-        <v>225704</v>
+        <v>194696</v>
       </c>
       <c r="I422">
         <v>-449440</v>
@@ -18851,8 +18851,8 @@
       <c r="K422">
         <v>76954</v>
       </c>
-      <c r="L422">
-        <v>8810.8</v>
+      <c r="L422" t="s">
+        <v>3</v>
       </c>
       <c r="M422">
         <v>400</v>
@@ -18878,13 +18878,13 @@
         <v>3</v>
       </c>
       <c r="F423">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G423">
         <v>700</v>
       </c>
       <c r="H423">
-        <v>225704</v>
+        <v>194696</v>
       </c>
       <c r="I423">
         <v>-449440</v>
@@ -18895,8 +18895,8 @@
       <c r="K423">
         <v>76954</v>
       </c>
-      <c r="L423">
-        <v>8810.8</v>
+      <c r="L423" t="s">
+        <v>3</v>
       </c>
       <c r="M423">
         <v>400</v>
@@ -18922,13 +18922,13 @@
         <v>3</v>
       </c>
       <c r="F424">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G424">
         <v>-700</v>
       </c>
       <c r="H424">
-        <v>224072</v>
+        <v>196328</v>
       </c>
       <c r="I424">
         <v>-458420</v>
@@ -18939,8 +18939,8 @@
       <c r="K424">
         <v>76954</v>
       </c>
-      <c r="L424">
-        <v>10888.8</v>
+      <c r="L424" t="s">
+        <v>3</v>
       </c>
       <c r="M424">
         <v>400</v>
@@ -18966,13 +18966,13 @@
         <v>3</v>
       </c>
       <c r="F425">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G425">
         <v>700</v>
       </c>
       <c r="H425">
-        <v>224072</v>
+        <v>196328</v>
       </c>
       <c r="I425">
         <v>-458420</v>
@@ -18983,8 +18983,8 @@
       <c r="K425">
         <v>76954</v>
       </c>
-      <c r="L425">
-        <v>10888.8</v>
+      <c r="L425" t="s">
+        <v>3</v>
       </c>
       <c r="M425">
         <v>400</v>
@@ -19010,13 +19010,13 @@
         <v>3</v>
       </c>
       <c r="F426">
-        <v>-398700</v>
+        <v>-403660</v>
       </c>
       <c r="G426">
         <v>-700</v>
       </c>
       <c r="H426">
-        <v>222440</v>
+        <v>197960</v>
       </c>
       <c r="I426">
         <v>-467400</v>
@@ -19027,8 +19027,8 @@
       <c r="K426">
         <v>76954</v>
       </c>
-      <c r="L426">
-        <v>12468.2</v>
+      <c r="L426" t="s">
+        <v>3</v>
       </c>
       <c r="M426">
         <v>400</v>
@@ -19054,13 +19054,13 @@
         <v>3</v>
       </c>
       <c r="F427">
-        <v>-398700</v>
+        <v>-403660</v>
       </c>
       <c r="G427">
         <v>700</v>
       </c>
       <c r="H427">
-        <v>222440</v>
+        <v>197960</v>
       </c>
       <c r="I427">
         <v>-467400</v>
@@ -19071,8 +19071,8 @@
       <c r="K427">
         <v>76954</v>
       </c>
-      <c r="L427">
-        <v>12468.2</v>
+      <c r="L427" t="s">
+        <v>3</v>
       </c>
       <c r="M427">
         <v>400</v>
@@ -19098,13 +19098,13 @@
         <v>3</v>
       </c>
       <c r="F428">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G428">
         <v>-700</v>
       </c>
       <c r="H428">
-        <v>220808</v>
+        <v>199592</v>
       </c>
       <c r="I428">
         <v>-476380</v>
@@ -19115,8 +19115,8 @@
       <c r="K428">
         <v>76954</v>
       </c>
-      <c r="L428">
-        <v>5861.3</v>
+      <c r="L428" t="s">
+        <v>3</v>
       </c>
       <c r="M428">
         <v>400</v>
@@ -19142,13 +19142,13 @@
         <v>3</v>
       </c>
       <c r="F429">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G429">
         <v>700</v>
       </c>
       <c r="H429">
-        <v>220808</v>
+        <v>199592</v>
       </c>
       <c r="I429">
         <v>-476380</v>
@@ -19159,8 +19159,8 @@
       <c r="K429">
         <v>76954</v>
       </c>
-      <c r="L429">
-        <v>5861.3</v>
+      <c r="L429" t="s">
+        <v>3</v>
       </c>
       <c r="M429">
         <v>400</v>
@@ -19186,13 +19186,13 @@
         <v>3</v>
       </c>
       <c r="F430">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G430">
         <v>-700</v>
       </c>
       <c r="H430">
-        <v>219176</v>
+        <v>201224</v>
       </c>
       <c r="I430">
         <v>-485360</v>
@@ -19203,8 +19203,8 @@
       <c r="K430">
         <v>76954</v>
       </c>
-      <c r="L430">
-        <v>7805.8</v>
+      <c r="L430" t="s">
+        <v>3</v>
       </c>
       <c r="M430">
         <v>400</v>
@@ -19230,13 +19230,13 @@
         <v>3</v>
       </c>
       <c r="F431">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G431">
         <v>700</v>
       </c>
       <c r="H431">
-        <v>219176</v>
+        <v>201224</v>
       </c>
       <c r="I431">
         <v>-485360</v>
@@ -19247,8 +19247,8 @@
       <c r="K431">
         <v>76954</v>
       </c>
-      <c r="L431">
-        <v>7805.8</v>
+      <c r="L431" t="s">
+        <v>3</v>
       </c>
       <c r="M431">
         <v>400</v>
@@ -19274,13 +19274,13 @@
         <v>3</v>
       </c>
       <c r="F432">
-        <v>-398700</v>
+        <v>-403660</v>
       </c>
       <c r="G432">
         <v>-700</v>
       </c>
       <c r="H432">
-        <v>217544</v>
+        <v>202856</v>
       </c>
       <c r="I432">
         <v>-494340</v>
@@ -19291,8 +19291,8 @@
       <c r="K432">
         <v>76954</v>
       </c>
-      <c r="L432">
-        <v>9460.9</v>
+      <c r="L432" t="s">
+        <v>3</v>
       </c>
       <c r="M432">
         <v>400</v>
@@ -19318,13 +19318,13 @@
         <v>3</v>
       </c>
       <c r="F433">
-        <v>-398700</v>
+        <v>-403660</v>
       </c>
       <c r="G433">
         <v>700</v>
       </c>
       <c r="H433">
-        <v>217544</v>
+        <v>202856</v>
       </c>
       <c r="I433">
         <v>-494340</v>
@@ -19335,8 +19335,8 @@
       <c r="K433">
         <v>76954</v>
       </c>
-      <c r="L433">
-        <v>9460.9</v>
+      <c r="L433" t="s">
+        <v>3</v>
       </c>
       <c r="M433">
         <v>400</v>
@@ -19362,13 +19362,13 @@
         <v>3</v>
       </c>
       <c r="F434">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G434">
         <v>-700</v>
       </c>
       <c r="H434">
-        <v>215912</v>
+        <v>204488</v>
       </c>
       <c r="I434">
         <v>-503320</v>
@@ -19379,8 +19379,8 @@
       <c r="K434">
         <v>76954</v>
       </c>
-      <c r="L434">
-        <v>4580.2</v>
+      <c r="L434" t="s">
+        <v>3</v>
       </c>
       <c r="M434">
         <v>400</v>
@@ -19406,13 +19406,13 @@
         <v>3</v>
       </c>
       <c r="F435">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G435">
         <v>700</v>
       </c>
       <c r="H435">
-        <v>215912</v>
+        <v>204488</v>
       </c>
       <c r="I435">
         <v>-503320</v>
@@ -19423,8 +19423,8 @@
       <c r="K435">
         <v>76954</v>
       </c>
-      <c r="L435">
-        <v>4580.2</v>
+      <c r="L435" t="s">
+        <v>3</v>
       </c>
       <c r="M435">
         <v>400</v>
@@ -19450,13 +19450,13 @@
         <v>3</v>
       </c>
       <c r="F436">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G436">
         <v>-700</v>
       </c>
       <c r="H436">
-        <v>214280</v>
+        <v>206120</v>
       </c>
       <c r="I436">
         <v>-512300</v>
@@ -19467,8 +19467,8 @@
       <c r="K436">
         <v>76954</v>
       </c>
-      <c r="L436">
-        <v>6342.1</v>
+      <c r="L436" t="s">
+        <v>3</v>
       </c>
       <c r="M436">
         <v>400</v>
@@ -19494,13 +19494,13 @@
         <v>3</v>
       </c>
       <c r="F437">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G437">
         <v>700</v>
       </c>
       <c r="H437">
-        <v>214280</v>
+        <v>206120</v>
       </c>
       <c r="I437">
         <v>-512300</v>
@@ -19511,8 +19511,8 @@
       <c r="K437">
         <v>76954</v>
       </c>
-      <c r="L437">
-        <v>6342.1</v>
+      <c r="L437" t="s">
+        <v>3</v>
       </c>
       <c r="M437">
         <v>400</v>
@@ -19538,13 +19538,13 @@
         <v>3</v>
       </c>
       <c r="F438">
-        <v>-398700</v>
+        <v>-403660</v>
       </c>
       <c r="G438">
         <v>-700</v>
       </c>
       <c r="H438">
-        <v>212648</v>
+        <v>207752</v>
       </c>
       <c r="I438">
         <v>-521280</v>
@@ -19555,8 +19555,8 @@
       <c r="K438">
         <v>76954</v>
       </c>
-      <c r="L438">
-        <v>7934.1</v>
+      <c r="L438" t="s">
+        <v>3</v>
       </c>
       <c r="M438">
         <v>400</v>
@@ -19582,13 +19582,13 @@
         <v>3</v>
       </c>
       <c r="F439">
-        <v>-398700</v>
+        <v>-403660</v>
       </c>
       <c r="G439">
         <v>700</v>
       </c>
       <c r="H439">
-        <v>212648</v>
+        <v>207752</v>
       </c>
       <c r="I439">
         <v>-521280</v>
@@ -19599,8 +19599,8 @@
       <c r="K439">
         <v>76954</v>
       </c>
-      <c r="L439">
-        <v>7934.1</v>
+      <c r="L439" t="s">
+        <v>3</v>
       </c>
       <c r="M439">
         <v>400</v>
@@ -19626,13 +19626,13 @@
         <v>3</v>
       </c>
       <c r="F440">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G440">
         <v>-700</v>
       </c>
       <c r="H440">
-        <v>211016</v>
+        <v>209384</v>
       </c>
       <c r="I440">
         <v>-530260</v>
@@ -19643,8 +19643,8 @@
       <c r="K440">
         <v>76954</v>
       </c>
-      <c r="L440">
-        <v>3907.8</v>
+      <c r="L440" t="s">
+        <v>3</v>
       </c>
       <c r="M440">
         <v>400</v>
@@ -19670,13 +19670,13 @@
         <v>3</v>
       </c>
       <c r="F441">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G441">
         <v>700</v>
       </c>
       <c r="H441">
-        <v>211016</v>
+        <v>209384</v>
       </c>
       <c r="I441">
         <v>-530260</v>
@@ -19687,8 +19687,8 @@
       <c r="K441">
         <v>76954</v>
       </c>
-      <c r="L441">
-        <v>3907.8</v>
+      <c r="L441" t="s">
+        <v>3</v>
       </c>
       <c r="M441">
         <v>400</v>
@@ -19714,13 +19714,13 @@
         <v>3</v>
       </c>
       <c r="F442">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G442">
         <v>-700</v>
       </c>
       <c r="H442">
-        <v>209384</v>
+        <v>211016</v>
       </c>
       <c r="I442">
         <v>-539240</v>
@@ -19731,8 +19731,8 @@
       <c r="K442">
         <v>76954</v>
       </c>
-      <c r="L442">
-        <v>5537.7</v>
+      <c r="L442" t="s">
+        <v>3</v>
       </c>
       <c r="M442">
         <v>400</v>
@@ -19758,13 +19758,13 @@
         <v>3</v>
       </c>
       <c r="F443">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G443">
         <v>700</v>
       </c>
       <c r="H443">
-        <v>209384</v>
+        <v>211016</v>
       </c>
       <c r="I443">
         <v>-539240</v>
@@ -19775,8 +19775,8 @@
       <c r="K443">
         <v>76954</v>
       </c>
-      <c r="L443">
-        <v>5537.7</v>
+      <c r="L443" t="s">
+        <v>3</v>
       </c>
       <c r="M443">
         <v>400</v>
@@ -19802,13 +19802,13 @@
         <v>3</v>
       </c>
       <c r="F444">
-        <v>-398700</v>
+        <v>-403660</v>
       </c>
       <c r="G444">
         <v>-700</v>
       </c>
       <c r="H444">
-        <v>207752</v>
+        <v>212648</v>
       </c>
       <c r="I444">
         <v>-548220</v>
@@ -19819,8 +19819,8 @@
       <c r="K444">
         <v>76954</v>
       </c>
-      <c r="L444">
-        <v>7062.6</v>
+      <c r="L444" t="s">
+        <v>3</v>
       </c>
       <c r="M444">
         <v>400</v>
@@ -19846,13 +19846,13 @@
         <v>3</v>
       </c>
       <c r="F445">
-        <v>-398700</v>
+        <v>-403660</v>
       </c>
       <c r="G445">
         <v>700</v>
       </c>
       <c r="H445">
-        <v>207752</v>
+        <v>212648</v>
       </c>
       <c r="I445">
         <v>-548220</v>
@@ -19863,8 +19863,8 @@
       <c r="K445">
         <v>76954</v>
       </c>
-      <c r="L445">
-        <v>7062.6</v>
+      <c r="L445" t="s">
+        <v>3</v>
       </c>
       <c r="M445">
         <v>400</v>
@@ -19890,13 +19890,13 @@
         <v>3</v>
       </c>
       <c r="F446">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G446">
         <v>-700</v>
       </c>
       <c r="H446">
-        <v>206120</v>
+        <v>214280</v>
       </c>
       <c r="I446">
         <v>-557200</v>
@@ -19907,8 +19907,8 @@
       <c r="K446">
         <v>76954</v>
       </c>
-      <c r="L446">
-        <v>3516.3</v>
+      <c r="L446" t="s">
+        <v>3</v>
       </c>
       <c r="M446">
         <v>400</v>
@@ -19934,13 +19934,13 @@
         <v>3</v>
       </c>
       <c r="F447">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G447">
         <v>700</v>
       </c>
       <c r="H447">
-        <v>206120</v>
+        <v>214280</v>
       </c>
       <c r="I447">
         <v>-557200</v>
@@ -19951,8 +19951,8 @@
       <c r="K447">
         <v>76954</v>
       </c>
-      <c r="L447">
-        <v>3516.3</v>
+      <c r="L447" t="s">
+        <v>3</v>
       </c>
       <c r="M447">
         <v>400</v>
@@ -19978,13 +19978,13 @@
         <v>3</v>
       </c>
       <c r="F448">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G448">
         <v>-700</v>
       </c>
       <c r="H448">
-        <v>204488</v>
+        <v>215912</v>
       </c>
       <c r="I448">
         <v>-566180</v>
@@ -19995,8 +19995,8 @@
       <c r="K448">
         <v>76954</v>
       </c>
-      <c r="L448">
-        <v>5055.6</v>
+      <c r="L448" t="s">
+        <v>3</v>
       </c>
       <c r="M448">
         <v>400</v>
@@ -20022,13 +20022,13 @@
         <v>3</v>
       </c>
       <c r="F449">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G449">
         <v>700</v>
       </c>
       <c r="H449">
-        <v>204488</v>
+        <v>215912</v>
       </c>
       <c r="I449">
         <v>-566180</v>
@@ -20039,8 +20039,8 @@
       <c r="K449">
         <v>76954</v>
       </c>
-      <c r="L449">
-        <v>5055.6</v>
+      <c r="L449" t="s">
+        <v>3</v>
       </c>
       <c r="M449">
         <v>400</v>
@@ -20066,13 +20066,13 @@
         <v>3</v>
       </c>
       <c r="F450">
-        <v>-398700</v>
+        <v>-403660</v>
       </c>
       <c r="G450">
         <v>-700</v>
       </c>
       <c r="H450">
-        <v>202856</v>
+        <v>217544</v>
       </c>
       <c r="I450">
         <v>-575160</v>
@@ -20083,8 +20083,8 @@
       <c r="K450">
         <v>76954</v>
       </c>
-      <c r="L450">
-        <v>6526.9</v>
+      <c r="L450" t="s">
+        <v>3</v>
       </c>
       <c r="M450">
         <v>400</v>
@@ -20110,13 +20110,13 @@
         <v>3</v>
       </c>
       <c r="F451">
-        <v>-398700</v>
+        <v>-403660</v>
       </c>
       <c r="G451">
         <v>700</v>
       </c>
       <c r="H451">
-        <v>202856</v>
+        <v>217544</v>
       </c>
       <c r="I451">
         <v>-575160</v>
@@ -20127,8 +20127,8 @@
       <c r="K451">
         <v>76954</v>
       </c>
-      <c r="L451">
-        <v>6526.9</v>
+      <c r="L451" t="s">
+        <v>3</v>
       </c>
       <c r="M451">
         <v>400</v>
@@ -20154,13 +20154,13 @@
         <v>3</v>
       </c>
       <c r="F452">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G452">
         <v>-700</v>
       </c>
       <c r="H452">
-        <v>201224</v>
+        <v>219176</v>
       </c>
       <c r="I452">
         <v>-584140</v>
@@ -20171,8 +20171,8 @@
       <c r="K452">
         <v>76954</v>
       </c>
-      <c r="L452">
-        <v>3272.4</v>
+      <c r="L452" t="s">
+        <v>3</v>
       </c>
       <c r="M452">
         <v>400</v>
@@ -20198,13 +20198,13 @@
         <v>3</v>
       </c>
       <c r="F453">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G453">
         <v>700</v>
       </c>
       <c r="H453">
-        <v>201224</v>
+        <v>219176</v>
       </c>
       <c r="I453">
         <v>-584140</v>
@@ -20215,8 +20215,8 @@
       <c r="K453">
         <v>76954</v>
       </c>
-      <c r="L453">
-        <v>3272.4</v>
+      <c r="L453" t="s">
+        <v>3</v>
       </c>
       <c r="M453">
         <v>400</v>
@@ -20242,13 +20242,13 @@
         <v>3</v>
       </c>
       <c r="F454">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G454">
         <v>-700</v>
       </c>
       <c r="H454">
-        <v>199592</v>
+        <v>220808</v>
       </c>
       <c r="I454">
         <v>-593120</v>
@@ -20259,8 +20259,8 @@
       <c r="K454">
         <v>76954</v>
       </c>
-      <c r="L454">
-        <v>4749</v>
+      <c r="L454" t="s">
+        <v>3</v>
       </c>
       <c r="M454">
         <v>400</v>
@@ -20286,13 +20286,13 @@
         <v>3</v>
       </c>
       <c r="F455">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G455">
         <v>700</v>
       </c>
       <c r="H455">
-        <v>199592</v>
+        <v>220808</v>
       </c>
       <c r="I455">
         <v>-593120</v>
@@ -20303,8 +20303,8 @@
       <c r="K455">
         <v>76954</v>
       </c>
-      <c r="L455">
-        <v>4749</v>
+      <c r="L455" t="s">
+        <v>3</v>
       </c>
       <c r="M455">
         <v>400</v>
@@ -20330,13 +20330,13 @@
         <v>3</v>
       </c>
       <c r="F456">
-        <v>-398700</v>
+        <v>-403660</v>
       </c>
       <c r="G456">
         <v>-700</v>
       </c>
       <c r="H456">
-        <v>197960</v>
+        <v>222440</v>
       </c>
       <c r="I456">
         <v>-602100</v>
@@ -20347,8 +20347,8 @@
       <c r="K456">
         <v>76954</v>
       </c>
-      <c r="L456">
-        <v>6179.9</v>
+      <c r="L456" t="s">
+        <v>3</v>
       </c>
       <c r="M456">
         <v>400</v>
@@ -20374,13 +20374,13 @@
         <v>3</v>
       </c>
       <c r="F457">
-        <v>-398700</v>
+        <v>-403660</v>
       </c>
       <c r="G457">
         <v>700</v>
       </c>
       <c r="H457">
-        <v>197960</v>
+        <v>222440</v>
       </c>
       <c r="I457">
         <v>-602100</v>
@@ -20391,8 +20391,8 @@
       <c r="K457">
         <v>76954</v>
       </c>
-      <c r="L457">
-        <v>6179.9</v>
+      <c r="L457" t="s">
+        <v>3</v>
       </c>
       <c r="M457">
         <v>400</v>
@@ -20418,13 +20418,13 @@
         <v>3</v>
       </c>
       <c r="F458">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G458">
         <v>-700</v>
       </c>
       <c r="H458">
-        <v>196328</v>
+        <v>224072</v>
       </c>
       <c r="I458">
         <v>-611080</v>
@@ -20435,8 +20435,8 @@
       <c r="K458">
         <v>76954</v>
       </c>
-      <c r="L458">
-        <v>3112.8</v>
+      <c r="L458" t="s">
+        <v>3</v>
       </c>
       <c r="M458">
         <v>400</v>
@@ -20462,13 +20462,13 @@
         <v>3</v>
       </c>
       <c r="F459">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G459">
         <v>700</v>
       </c>
       <c r="H459">
-        <v>196328</v>
+        <v>224072</v>
       </c>
       <c r="I459">
         <v>-611080</v>
@@ -20479,8 +20479,8 @@
       <c r="K459">
         <v>76954</v>
       </c>
-      <c r="L459">
-        <v>3112.8</v>
+      <c r="L459" t="s">
+        <v>3</v>
       </c>
       <c r="M459">
         <v>400</v>
@@ -20506,13 +20506,13 @@
         <v>3</v>
       </c>
       <c r="F460">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G460">
         <v>-700</v>
       </c>
       <c r="H460">
-        <v>194696</v>
+        <v>225704</v>
       </c>
       <c r="I460">
         <v>-620060</v>
@@ -20523,8 +20523,8 @@
       <c r="K460">
         <v>76954</v>
       </c>
-      <c r="L460">
-        <v>4545.1</v>
+      <c r="L460" t="s">
+        <v>3</v>
       </c>
       <c r="M460">
         <v>400</v>
@@ -20550,13 +20550,13 @@
         <v>3</v>
       </c>
       <c r="F461">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G461">
         <v>700</v>
       </c>
       <c r="H461">
-        <v>194696</v>
+        <v>225704</v>
       </c>
       <c r="I461">
         <v>-620060</v>
@@ -20567,8 +20567,8 @@
       <c r="K461">
         <v>76954</v>
       </c>
-      <c r="L461">
-        <v>4545.1</v>
+      <c r="L461" t="s">
+        <v>3</v>
       </c>
       <c r="M461">
         <v>400</v>
@@ -20594,13 +20594,13 @@
         <v>3</v>
       </c>
       <c r="F462">
-        <v>-398700</v>
+        <v>-403660</v>
       </c>
       <c r="G462">
         <v>-700</v>
       </c>
       <c r="H462">
-        <v>193064</v>
+        <v>227336</v>
       </c>
       <c r="I462">
         <v>-629040</v>
@@ -20611,8 +20611,8 @@
       <c r="K462">
         <v>76954</v>
       </c>
-      <c r="L462">
-        <v>5945.7</v>
+      <c r="L462" t="s">
+        <v>3</v>
       </c>
       <c r="M462">
         <v>400</v>
@@ -20638,13 +20638,13 @@
         <v>3</v>
       </c>
       <c r="F463">
-        <v>-398700</v>
+        <v>-403660</v>
       </c>
       <c r="G463">
         <v>700</v>
       </c>
       <c r="H463">
-        <v>193064</v>
+        <v>227336</v>
       </c>
       <c r="I463">
         <v>-629040</v>
@@ -20655,8 +20655,8 @@
       <c r="K463">
         <v>76954</v>
       </c>
-      <c r="L463">
-        <v>5945.7</v>
+      <c r="L463" t="s">
+        <v>3</v>
       </c>
       <c r="M463">
         <v>400</v>
@@ -20682,13 +20682,13 @@
         <v>3</v>
       </c>
       <c r="F464">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G464">
         <v>-700</v>
       </c>
       <c r="H464">
-        <v>191432</v>
+        <v>228968</v>
       </c>
       <c r="I464">
         <v>-638020</v>
@@ -20699,8 +20699,8 @@
       <c r="K464">
         <v>76954</v>
       </c>
-      <c r="L464">
-        <v>3004.2</v>
+      <c r="L464" t="s">
+        <v>3</v>
       </c>
       <c r="M464">
         <v>400</v>
@@ -20726,13 +20726,13 @@
         <v>3</v>
       </c>
       <c r="F465">
-        <v>-401300</v>
+        <v>-403660</v>
       </c>
       <c r="G465">
         <v>700</v>
       </c>
       <c r="H465">
-        <v>191432</v>
+        <v>228968</v>
       </c>
       <c r="I465">
         <v>-638020</v>
@@ -20743,8 +20743,8 @@
       <c r="K465">
         <v>76954</v>
       </c>
-      <c r="L465">
-        <v>3004.2</v>
+      <c r="L465" t="s">
+        <v>3</v>
       </c>
       <c r="M465">
         <v>400</v>
@@ -20770,13 +20770,13 @@
         <v>3</v>
       </c>
       <c r="F466">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G466">
         <v>-700</v>
       </c>
       <c r="H466">
-        <v>189800</v>
+        <v>230600</v>
       </c>
       <c r="I466">
         <v>-647000</v>
@@ -20787,8 +20787,8 @@
       <c r="K466">
         <v>76954</v>
       </c>
-      <c r="L466">
-        <v>4404.7</v>
+      <c r="L466" t="s">
+        <v>3</v>
       </c>
       <c r="M466">
         <v>400</v>
@@ -20814,13 +20814,13 @@
         <v>3</v>
       </c>
       <c r="F467">
-        <v>-400000</v>
+        <v>-403660</v>
       </c>
       <c r="G467">
         <v>700</v>
       </c>
       <c r="H467">
-        <v>189800</v>
+        <v>230600</v>
       </c>
       <c r="I467">
         <v>-647000</v>
@@ -20831,8 +20831,8 @@
       <c r="K467">
         <v>76954</v>
       </c>
-      <c r="L467">
-        <v>4404.7</v>
+      <c r="L467" t="s">
+        <v>3</v>
       </c>
       <c r="M467">
         <v>400</v>
@@ -21688,13 +21688,13 @@
         <v>103</v>
       </c>
       <c r="F500">
-        <v>-400000</v>
+        <v>-396340</v>
       </c>
       <c r="G500">
         <v>-700</v>
       </c>
       <c r="H500">
-        <v>209384</v>
+        <v>211016</v>
       </c>
     </row>
     <row r="501" spans="1:9" x14ac:dyDescent="0.25">

--- a/plate3d/PLATE3D_INCHEON.xlsx
+++ b/plate3d/PLATE3D_INCHEON.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3644" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3644" uniqueCount="124">
   <si>
-    <t>30 m at the footing, 26 m at 60 m, then to the shaft at 175 m: 45,050 where the deck goes through</t>
+    <t>INCHEON BRIDGE  ·  800 m main span, 230.5 m pylons, 208 stays  ·  mm, Z up</t>
   </si>
   <si>
     <t>COORD</t>
@@ -238,6 +238,9 @@
     <t>ONE PYLON - two legs that flow into one box, not two boxes that step</t>
   </si>
   <si>
+    <t>32 m apart at the footing, 45 m at the crossbeam, then one shaft: a lozenge, not a Y</t>
+  </si>
+  <si>
     <t>md.pyl</t>
   </si>
   <si>
@@ -253,7 +256,7 @@
     <t>md.stay</t>
   </si>
   <si>
-    <t>sc.ca_1</t>
+    <t>sc.cb_1</t>
   </si>
   <si>
     <t>PIERS W2 AND W3 - under the side span and under the end of the deck</t>
@@ -16103,7 +16106,7 @@
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>51</v>
@@ -16153,7 +16156,7 @@
         <v>63</v>
       </c>
       <c r="C361" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D361" t="s">
         <v>46</v>
@@ -16197,7 +16200,7 @@
         <v>63</v>
       </c>
       <c r="C362" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D362" t="s">
         <v>47</v>
@@ -16241,7 +16244,7 @@
         <v>63</v>
       </c>
       <c r="C363" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D363" t="s">
         <v>46</v>
@@ -16285,7 +16288,7 @@
         <v>63</v>
       </c>
       <c r="C364" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D364" t="s">
         <v>47</v>
@@ -16329,7 +16332,7 @@
         <v>63</v>
       </c>
       <c r="C365" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D365" t="s">
         <v>48</v>
@@ -16373,7 +16376,7 @@
         <v>63</v>
       </c>
       <c r="C366" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D366" t="s">
         <v>35</v>
@@ -16417,7 +16420,7 @@
         <v>63</v>
       </c>
       <c r="C367" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D367" t="s">
         <v>36</v>
@@ -16499,13 +16502,13 @@
         <v>63</v>
       </c>
       <c r="C369" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D369" t="s">
         <v>72</v>
       </c>
       <c r="E369" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F369" t="s">
         <v>22</v>
@@ -16519,12 +16522,12 @@
         <v>49</v>
       </c>
       <c r="C371" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>51</v>
@@ -16574,7 +16577,7 @@
         <v>63</v>
       </c>
       <c r="C373" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D373" t="s">
         <v>23</v>
@@ -16618,7 +16621,7 @@
         <v>63</v>
       </c>
       <c r="C374" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D374" t="s">
         <v>23</v>
@@ -16662,7 +16665,7 @@
         <v>63</v>
       </c>
       <c r="C375" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D375" t="s">
         <v>23</v>
@@ -16706,7 +16709,7 @@
         <v>63</v>
       </c>
       <c r="C376" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D376" t="s">
         <v>23</v>
@@ -16750,7 +16753,7 @@
         <v>63</v>
       </c>
       <c r="C377" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D377" t="s">
         <v>23</v>
@@ -16794,7 +16797,7 @@
         <v>63</v>
       </c>
       <c r="C378" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D378" t="s">
         <v>23</v>
@@ -16838,7 +16841,7 @@
         <v>63</v>
       </c>
       <c r="C379" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D379" t="s">
         <v>23</v>
@@ -16882,7 +16885,7 @@
         <v>63</v>
       </c>
       <c r="C380" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D380" t="s">
         <v>23</v>
@@ -16926,7 +16929,7 @@
         <v>63</v>
       </c>
       <c r="C381" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D381" t="s">
         <v>23</v>
@@ -16970,7 +16973,7 @@
         <v>63</v>
       </c>
       <c r="C382" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D382" t="s">
         <v>23</v>
@@ -17014,7 +17017,7 @@
         <v>63</v>
       </c>
       <c r="C383" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D383" t="s">
         <v>23</v>
@@ -17058,7 +17061,7 @@
         <v>63</v>
       </c>
       <c r="C384" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D384" t="s">
         <v>23</v>
@@ -17102,7 +17105,7 @@
         <v>63</v>
       </c>
       <c r="C385" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D385" t="s">
         <v>23</v>
@@ -17146,7 +17149,7 @@
         <v>63</v>
       </c>
       <c r="C386" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D386" t="s">
         <v>23</v>
@@ -17190,7 +17193,7 @@
         <v>63</v>
       </c>
       <c r="C387" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D387" t="s">
         <v>23</v>
@@ -17234,7 +17237,7 @@
         <v>63</v>
       </c>
       <c r="C388" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D388" t="s">
         <v>23</v>
@@ -17278,7 +17281,7 @@
         <v>63</v>
       </c>
       <c r="C389" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D389" t="s">
         <v>23</v>
@@ -17322,7 +17325,7 @@
         <v>63</v>
       </c>
       <c r="C390" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D390" t="s">
         <v>23</v>
@@ -17366,7 +17369,7 @@
         <v>63</v>
       </c>
       <c r="C391" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D391" t="s">
         <v>23</v>
@@ -17410,7 +17413,7 @@
         <v>63</v>
       </c>
       <c r="C392" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D392" t="s">
         <v>23</v>
@@ -17454,7 +17457,7 @@
         <v>63</v>
       </c>
       <c r="C393" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D393" t="s">
         <v>23</v>
@@ -17498,7 +17501,7 @@
         <v>63</v>
       </c>
       <c r="C394" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D394" t="s">
         <v>23</v>
@@ -17542,7 +17545,7 @@
         <v>63</v>
       </c>
       <c r="C395" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D395" t="s">
         <v>23</v>
@@ -17586,7 +17589,7 @@
         <v>63</v>
       </c>
       <c r="C396" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D396" t="s">
         <v>23</v>
@@ -17630,7 +17633,7 @@
         <v>63</v>
       </c>
       <c r="C397" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D397" t="s">
         <v>23</v>
@@ -17674,7 +17677,7 @@
         <v>63</v>
       </c>
       <c r="C398" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D398" t="s">
         <v>23</v>
@@ -17718,7 +17721,7 @@
         <v>63</v>
       </c>
       <c r="C399" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D399" t="s">
         <v>19</v>
@@ -17762,7 +17765,7 @@
         <v>63</v>
       </c>
       <c r="C400" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D400" t="s">
         <v>19</v>
@@ -17806,7 +17809,7 @@
         <v>63</v>
       </c>
       <c r="C401" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D401" t="s">
         <v>19</v>
@@ -17850,7 +17853,7 @@
         <v>63</v>
       </c>
       <c r="C402" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D402" t="s">
         <v>19</v>
@@ -17894,7 +17897,7 @@
         <v>63</v>
       </c>
       <c r="C403" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D403" t="s">
         <v>19</v>
@@ -17938,7 +17941,7 @@
         <v>63</v>
       </c>
       <c r="C404" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D404" t="s">
         <v>19</v>
@@ -17982,7 +17985,7 @@
         <v>63</v>
       </c>
       <c r="C405" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D405" t="s">
         <v>19</v>
@@ -18026,7 +18029,7 @@
         <v>63</v>
       </c>
       <c r="C406" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D406" t="s">
         <v>19</v>
@@ -18070,7 +18073,7 @@
         <v>63</v>
       </c>
       <c r="C407" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D407" t="s">
         <v>19</v>
@@ -18114,7 +18117,7 @@
         <v>63</v>
       </c>
       <c r="C408" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D408" t="s">
         <v>19</v>
@@ -18158,7 +18161,7 @@
         <v>63</v>
       </c>
       <c r="C409" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D409" t="s">
         <v>19</v>
@@ -18202,7 +18205,7 @@
         <v>63</v>
       </c>
       <c r="C410" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D410" t="s">
         <v>19</v>
@@ -18246,7 +18249,7 @@
         <v>63</v>
       </c>
       <c r="C411" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D411" t="s">
         <v>19</v>
@@ -18290,7 +18293,7 @@
         <v>63</v>
       </c>
       <c r="C412" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D412" t="s">
         <v>19</v>
@@ -18334,7 +18337,7 @@
         <v>63</v>
       </c>
       <c r="C413" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D413" t="s">
         <v>19</v>
@@ -18378,7 +18381,7 @@
         <v>63</v>
       </c>
       <c r="C414" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D414" t="s">
         <v>19</v>
@@ -18422,7 +18425,7 @@
         <v>63</v>
       </c>
       <c r="C415" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D415" t="s">
         <v>19</v>
@@ -18466,7 +18469,7 @@
         <v>63</v>
       </c>
       <c r="C416" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D416" t="s">
         <v>19</v>
@@ -18510,7 +18513,7 @@
         <v>63</v>
       </c>
       <c r="C417" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D417" t="s">
         <v>19</v>
@@ -18554,7 +18557,7 @@
         <v>63</v>
       </c>
       <c r="C418" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D418" t="s">
         <v>19</v>
@@ -18598,7 +18601,7 @@
         <v>63</v>
       </c>
       <c r="C419" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D419" t="s">
         <v>19</v>
@@ -18642,7 +18645,7 @@
         <v>63</v>
       </c>
       <c r="C420" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D420" t="s">
         <v>19</v>
@@ -18686,7 +18689,7 @@
         <v>63</v>
       </c>
       <c r="C421" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D421" t="s">
         <v>19</v>
@@ -18730,7 +18733,7 @@
         <v>63</v>
       </c>
       <c r="C422" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D422" t="s">
         <v>19</v>
@@ -18774,7 +18777,7 @@
         <v>63</v>
       </c>
       <c r="C423" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D423" t="s">
         <v>19</v>
@@ -18818,7 +18821,7 @@
         <v>63</v>
       </c>
       <c r="C424" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D424" t="s">
         <v>19</v>
@@ -18862,7 +18865,7 @@
         <v>63</v>
       </c>
       <c r="C425" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D425" t="s">
         <v>19</v>
@@ -18906,7 +18909,7 @@
         <v>63</v>
       </c>
       <c r="C426" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D426" t="s">
         <v>19</v>
@@ -18950,7 +18953,7 @@
         <v>63</v>
       </c>
       <c r="C427" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D427" t="s">
         <v>19</v>
@@ -18994,7 +18997,7 @@
         <v>63</v>
       </c>
       <c r="C428" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D428" t="s">
         <v>19</v>
@@ -19038,7 +19041,7 @@
         <v>63</v>
       </c>
       <c r="C429" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D429" t="s">
         <v>19</v>
@@ -19082,7 +19085,7 @@
         <v>63</v>
       </c>
       <c r="C430" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D430" t="s">
         <v>19</v>
@@ -19126,7 +19129,7 @@
         <v>63</v>
       </c>
       <c r="C431" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D431" t="s">
         <v>19</v>
@@ -19170,7 +19173,7 @@
         <v>63</v>
       </c>
       <c r="C432" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D432" t="s">
         <v>19</v>
@@ -19214,7 +19217,7 @@
         <v>63</v>
       </c>
       <c r="C433" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D433" t="s">
         <v>19</v>
@@ -19258,7 +19261,7 @@
         <v>63</v>
       </c>
       <c r="C434" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D434" t="s">
         <v>19</v>
@@ -19302,7 +19305,7 @@
         <v>63</v>
       </c>
       <c r="C435" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D435" t="s">
         <v>19</v>
@@ -19346,7 +19349,7 @@
         <v>63</v>
       </c>
       <c r="C436" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D436" t="s">
         <v>19</v>
@@ -19390,7 +19393,7 @@
         <v>63</v>
       </c>
       <c r="C437" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D437" t="s">
         <v>19</v>
@@ -19434,7 +19437,7 @@
         <v>63</v>
       </c>
       <c r="C438" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D438" t="s">
         <v>19</v>
@@ -19478,7 +19481,7 @@
         <v>63</v>
       </c>
       <c r="C439" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D439" t="s">
         <v>19</v>
@@ -19522,7 +19525,7 @@
         <v>63</v>
       </c>
       <c r="C440" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D440" t="s">
         <v>19</v>
@@ -19566,7 +19569,7 @@
         <v>63</v>
       </c>
       <c r="C441" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D441" t="s">
         <v>19</v>
@@ -19610,7 +19613,7 @@
         <v>63</v>
       </c>
       <c r="C442" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D442" t="s">
         <v>19</v>
@@ -19654,7 +19657,7 @@
         <v>63</v>
       </c>
       <c r="C443" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D443" t="s">
         <v>19</v>
@@ -19698,7 +19701,7 @@
         <v>63</v>
       </c>
       <c r="C444" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D444" t="s">
         <v>19</v>
@@ -19742,7 +19745,7 @@
         <v>63</v>
       </c>
       <c r="C445" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D445" t="s">
         <v>19</v>
@@ -19786,7 +19789,7 @@
         <v>63</v>
       </c>
       <c r="C446" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D446" t="s">
         <v>19</v>
@@ -19830,7 +19833,7 @@
         <v>63</v>
       </c>
       <c r="C447" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D447" t="s">
         <v>19</v>
@@ -19874,7 +19877,7 @@
         <v>63</v>
       </c>
       <c r="C448" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D448" t="s">
         <v>19</v>
@@ -19918,7 +19921,7 @@
         <v>63</v>
       </c>
       <c r="C449" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D449" t="s">
         <v>19</v>
@@ -19962,7 +19965,7 @@
         <v>63</v>
       </c>
       <c r="C450" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D450" t="s">
         <v>19</v>
@@ -20006,7 +20009,7 @@
         <v>63</v>
       </c>
       <c r="C451" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D451" t="s">
         <v>19</v>
@@ -20050,7 +20053,7 @@
         <v>63</v>
       </c>
       <c r="C452" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D452" t="s">
         <v>19</v>
@@ -20094,7 +20097,7 @@
         <v>63</v>
       </c>
       <c r="C453" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D453" t="s">
         <v>19</v>
@@ -20138,7 +20141,7 @@
         <v>63</v>
       </c>
       <c r="C454" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D454" t="s">
         <v>19</v>
@@ -20182,7 +20185,7 @@
         <v>63</v>
       </c>
       <c r="C455" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D455" t="s">
         <v>19</v>
@@ -20226,7 +20229,7 @@
         <v>63</v>
       </c>
       <c r="C456" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D456" t="s">
         <v>19</v>
@@ -20270,7 +20273,7 @@
         <v>63</v>
       </c>
       <c r="C457" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D457" t="s">
         <v>19</v>
@@ -20314,7 +20317,7 @@
         <v>63</v>
       </c>
       <c r="C458" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D458" t="s">
         <v>19</v>
@@ -20358,7 +20361,7 @@
         <v>63</v>
       </c>
       <c r="C459" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D459" t="s">
         <v>19</v>
@@ -20402,7 +20405,7 @@
         <v>63</v>
       </c>
       <c r="C460" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D460" t="s">
         <v>19</v>
@@ -20446,7 +20449,7 @@
         <v>63</v>
       </c>
       <c r="C461" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D461" t="s">
         <v>19</v>
@@ -20490,7 +20493,7 @@
         <v>63</v>
       </c>
       <c r="C462" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D462" t="s">
         <v>19</v>
@@ -20534,7 +20537,7 @@
         <v>63</v>
       </c>
       <c r="C463" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D463" t="s">
         <v>19</v>
@@ -20578,7 +20581,7 @@
         <v>63</v>
       </c>
       <c r="C464" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D464" t="s">
         <v>19</v>
@@ -20622,7 +20625,7 @@
         <v>63</v>
       </c>
       <c r="C465" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D465" t="s">
         <v>19</v>
@@ -20666,7 +20669,7 @@
         <v>63</v>
       </c>
       <c r="C466" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D466" t="s">
         <v>19</v>
@@ -20710,7 +20713,7 @@
         <v>63</v>
       </c>
       <c r="C467" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D467" t="s">
         <v>19</v>
@@ -20754,7 +20757,7 @@
         <v>63</v>
       </c>
       <c r="C468" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D468" t="s">
         <v>19</v>
@@ -20798,7 +20801,7 @@
         <v>63</v>
       </c>
       <c r="C469" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D469" t="s">
         <v>19</v>
@@ -20842,7 +20845,7 @@
         <v>63</v>
       </c>
       <c r="C470" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D470" t="s">
         <v>19</v>
@@ -20886,7 +20889,7 @@
         <v>63</v>
       </c>
       <c r="C471" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D471" t="s">
         <v>19</v>
@@ -20930,7 +20933,7 @@
         <v>63</v>
       </c>
       <c r="C472" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D472" t="s">
         <v>19</v>
@@ -20974,7 +20977,7 @@
         <v>63</v>
       </c>
       <c r="C473" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D473" t="s">
         <v>19</v>
@@ -21018,7 +21021,7 @@
         <v>63</v>
       </c>
       <c r="C474" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D474" t="s">
         <v>19</v>
@@ -21062,7 +21065,7 @@
         <v>63</v>
       </c>
       <c r="C475" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D475" t="s">
         <v>19</v>
@@ -21106,7 +21109,7 @@
         <v>63</v>
       </c>
       <c r="C476" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D476" t="s">
         <v>19</v>
@@ -21188,13 +21191,13 @@
         <v>63</v>
       </c>
       <c r="C478" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D478" t="s">
         <v>72</v>
       </c>
       <c r="E478" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F478" t="s">
         <v>22</v>
@@ -21208,7 +21211,7 @@
         <v>49</v>
       </c>
       <c r="C480" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="481" spans="1:14" x14ac:dyDescent="0.25">
@@ -21263,7 +21266,7 @@
         <v>63</v>
       </c>
       <c r="C482" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D482" t="s">
         <v>37</v>
@@ -21307,7 +21310,7 @@
         <v>63</v>
       </c>
       <c r="C483" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D483" t="s">
         <v>37</v>
@@ -21351,7 +21354,7 @@
         <v>63</v>
       </c>
       <c r="C484" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D484" t="s">
         <v>37</v>
@@ -21395,7 +21398,7 @@
         <v>63</v>
       </c>
       <c r="C485" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D485" t="s">
         <v>37</v>
@@ -21439,7 +21442,7 @@
         <v>63</v>
       </c>
       <c r="C486" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D486" t="s">
         <v>36</v>
@@ -21483,7 +21486,7 @@
         <v>63</v>
       </c>
       <c r="C487" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D487" t="s">
         <v>36</v>
@@ -21565,13 +21568,13 @@
         <v>63</v>
       </c>
       <c r="C489" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D489" t="s">
         <v>72</v>
       </c>
       <c r="E489" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F489" t="s">
         <v>22</v>
@@ -21579,28 +21582,28 @@
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C491" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D491" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E491" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F491" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G491" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H491" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.25">
@@ -21608,13 +21611,13 @@
         <v>3</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C492" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D492" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E492" t="s">
         <v>3</v>
@@ -21626,7 +21629,7 @@
         <v>2000</v>
       </c>
       <c r="H492" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.25">
@@ -21634,13 +21637,13 @@
         <v>3</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C493" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D493" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E493" t="s">
         <v>3</v>
@@ -21652,7 +21655,7 @@
         <v>2000</v>
       </c>
       <c r="H493" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.25">
@@ -21660,13 +21663,13 @@
         <v>3</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C494" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D494" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E494" t="s">
         <v>3</v>
@@ -21678,7 +21681,7 @@
         <v>500</v>
       </c>
       <c r="H494" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.25">
@@ -21686,13 +21689,13 @@
         <v>3</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C495" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D495" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E495" t="s">
         <v>3</v>
@@ -21704,7 +21707,7 @@
         <v>500</v>
       </c>
       <c r="H495" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.25">
@@ -21712,13 +21715,13 @@
         <v>3</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C496" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D496" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E496" t="s">
         <v>3</v>
@@ -21730,7 +21733,7 @@
         <v>1000</v>
       </c>
       <c r="H496" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.25">
@@ -21738,13 +21741,13 @@
         <v>3</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C497" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D497" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E497" t="s">
         <v>3</v>
@@ -21756,7 +21759,7 @@
         <v>1000</v>
       </c>
       <c r="H497" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.25">
@@ -21764,13 +21767,13 @@
         <v>3</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C498" t="s">
         <v>64</v>
       </c>
       <c r="D498" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E498" t="s">
         <v>3</v>
@@ -21782,7 +21785,7 @@
         <v>200</v>
       </c>
       <c r="H498" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.25">
@@ -21790,13 +21793,13 @@
         <v>3</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C499" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D499" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E499" t="s">
         <v>3</v>
@@ -21808,33 +21811,33 @@
         <v>200</v>
       </c>
       <c r="H499" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B501" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C501" t="s">
         <v>5</v>
       </c>
       <c r="D501" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E501" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F501" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G501" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H501" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I501" t="s">
         <v>68</v>
@@ -21848,7 +21851,7 @@
         <v>49</v>
       </c>
       <c r="C502" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="503" spans="1:8" x14ac:dyDescent="0.25">
@@ -21856,16 +21859,16 @@
         <v>3</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C503" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D503" t="s">
         <v>64</v>
       </c>
       <c r="E503" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F503">
         <v>-740000</v>
@@ -21882,25 +21885,25 @@
         <v>3</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C505" t="s">
         <v>5</v>
       </c>
       <c r="D505" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E505" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F505" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G505" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H505" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I505" t="s">
         <v>68</v>
@@ -21914,7 +21917,7 @@
         <v>49</v>
       </c>
       <c r="C506" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.25">
@@ -21922,16 +21925,16 @@
         <v>3</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C507" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D507" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E507" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F507">
         <v>-400000</v>
@@ -21948,16 +21951,16 @@
         <v>3</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C508" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D508" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E508" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F508">
         <v>0</v>
@@ -21969,7 +21972,7 @@
         <v>0</v>
       </c>
       <c r="I508" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="509" spans="1:8" x14ac:dyDescent="0.25">
@@ -21977,25 +21980,25 @@
         <v>3</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C509" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D509" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E509" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F509">
-        <v>-396340</v>
+        <v>-396360</v>
       </c>
       <c r="G509">
         <v>-700</v>
       </c>
       <c r="H509">
-        <v>211016</v>
+        <v>189800</v>
       </c>
     </row>
     <row r="510" spans="1:9" x14ac:dyDescent="0.25">
@@ -22003,28 +22006,28 @@
         <v>3</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C510" t="s">
+        <v>121</v>
+      </c>
+      <c r="D510" t="s">
+        <v>121</v>
+      </c>
+      <c r="E510" t="s">
+        <v>119</v>
+      </c>
+      <c r="F510">
+        <v>0</v>
+      </c>
+      <c r="G510">
+        <v>0</v>
+      </c>
+      <c r="H510">
+        <v>0</v>
+      </c>
+      <c r="I510" t="s">
         <v>120</v>
-      </c>
-      <c r="D510" t="s">
-        <v>120</v>
-      </c>
-      <c r="E510" t="s">
-        <v>118</v>
-      </c>
-      <c r="F510">
-        <v>0</v>
-      </c>
-      <c r="G510">
-        <v>0</v>
-      </c>
-      <c r="H510">
-        <v>0</v>
-      </c>
-      <c r="I510" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="511" spans="1:8" x14ac:dyDescent="0.25">
@@ -22032,16 +22035,16 @@
         <v>3</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C511" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D511" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E511" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F511">
         <v>-660000</v>
@@ -22058,16 +22061,16 @@
         <v>3</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C512" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D512" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E512" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F512">
         <v>0</v>
@@ -22079,7 +22082,7 @@
         <v>0</v>
       </c>
       <c r="I512" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.25">
@@ -22087,7 +22090,7 @@
         <v>3</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
